--- a/TeacherTraining/templates/master-history-template.xlsx
+++ b/TeacherTraining/templates/master-history-template.xlsx
@@ -55,12 +55,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-04</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-10</t>
         </is>
       </c>
     </row>
